--- a/biljart moyenne - BU.xlsx
+++ b/biljart moyenne - BU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\MyTech\Github\biljart\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tenneteu-my.sharepoint.com/personal/sandjai_ramasray_tennet_eu/Documents/GithubCopilotWS/Biljart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F343C7-2C2A-471E-8BF8-C2B0160AD2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCF40FB0-13A8-4294-92A5-0863F341ED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14310" yWindow="945" windowWidth="21945" windowHeight="14415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15420" yWindow="1905" windowWidth="33105" windowHeight="19110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -80,11 +80,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -102,10 +104,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -143,7 +149,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -249,7 +255,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -391,7 +397,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -399,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -897,7 +903,153 @@
         <v>0.48</v>
       </c>
     </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>46157</v>
+      </c>
+      <c r="B31" s="4">
+        <v>0.43333333333333335</v>
+      </c>
+      <c r="C31" s="4">
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="D31" s="4">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E31" s="4">
+        <v>0.56666666666666665</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="C32" s="4">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0.43333333333333335</v>
+      </c>
+      <c r="E32" s="4">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="C33" s="4">
+        <v>0.43333333333333335</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0.43333333333333335</v>
+      </c>
+      <c r="E33" s="4">
+        <v>0.43333333333333335</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>46162</v>
+      </c>
+      <c r="B34" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="C34" s="4">
+        <v>0.24</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0.32</v>
+      </c>
+      <c r="E34" s="4">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="C35" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="D35" s="4">
+        <v>0.24</v>
+      </c>
+      <c r="E35" s="4">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>46234</v>
+      </c>
+      <c r="B36" s="4">
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="C36" s="4">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="D36" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="E36" s="4"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="C37" s="4">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D37" s="4">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
+        <v>46241</v>
+      </c>
+      <c r="B38" s="4">
+        <f>9/30</f>
+        <v>0.3</v>
+      </c>
+      <c r="C38" s="4">
+        <f>13/30</f>
+        <v>0.43333333333333335</v>
+      </c>
+      <c r="D38" s="4">
+        <f>14/30</f>
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="E38" s="4"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="5"/>
+      <c r="B39" s="4">
+        <f>14/30</f>
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="C39" s="4">
+        <f>14/30</f>
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="D39" s="4">
+        <f>9/30</f>
+        <v>0.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{6e118e09-08be-4360-a815-3fc29828016d}" enabled="1" method="Standard" siteId="{15b734ef-4a07-47e7-90f4-22cc84a7af23}" removed="0"/>
+</clbl:labelList>
 </file>